--- a/VerveStacks_SAU_grids_kan25/SysSettings.xlsx
+++ b/VerveStacks_SAU_grids_kan25/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SAU_grids_kan25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E490CF-294F-4069-B722-C76374F73B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA0CFBA-99E2-4686-B261-DDF5890FED01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1553,7 +1553,7 @@
     <t>e_SA12-380_SAU</t>
   </si>
   <si>
-    <t>grid node -- SA12-380</t>
+    <t>grid node -- SA12-380 (Tabuk, 18 km)</t>
   </si>
   <si>
     <t>lo</t>
@@ -1562,109 +1562,109 @@
     <t>e_SA4-380_SAU</t>
   </si>
   <si>
-    <t>grid node -- SA4-380</t>
+    <t>grid node -- SA4-380 (Rafha, 15 km)</t>
   </si>
   <si>
     <t>e_w115168488-380_SAU</t>
   </si>
   <si>
-    <t>grid node -- way/115168488-380</t>
+    <t>grid node -- way/115168488-380 (Mecca, 11 km)</t>
   </si>
   <si>
     <t>e_w1317464635-380_SAU</t>
   </si>
   <si>
-    <t>grid node -- way/1317464635-380</t>
+    <t>grid node -- way/1317464635-380 (Medina, 14 km)</t>
   </si>
   <si>
     <t>e_w181132741-380_SAU</t>
   </si>
   <si>
-    <t>grid node -- way/181132741-380</t>
+    <t>grid node -- way/181132741-380 (Ar Rass, 12 km)</t>
   </si>
   <si>
     <t>e_w198144511-230_SAU</t>
   </si>
   <si>
-    <t>grid node -- way/198144511-230</t>
+    <t>grid node -- way/198144511-230 (Al Jubayl, 9 km)</t>
   </si>
   <si>
     <t>e_w203627872-380_SAU</t>
   </si>
   <si>
-    <t>grid node -- way/203627872-380</t>
+    <t>grid node -- way/203627872-380 (Jeddah, 109 km)</t>
   </si>
   <si>
     <t>e_w204824991-380_SAU</t>
   </si>
   <si>
-    <t>grid node -- way/204824991-380</t>
+    <t>grid node -- way/204824991-380 (Abha, 22 km)</t>
   </si>
   <si>
     <t>e_w207785816-380_SAU</t>
   </si>
   <si>
-    <t>grid node -- way/207785816-380</t>
+    <t>grid node -- way/207785816-380 (Riyadh, 40 km)</t>
   </si>
   <si>
     <t>e_w524688755-380_SAU</t>
   </si>
   <si>
-    <t>grid node -- way/524688755-380</t>
+    <t>grid node -- way/524688755-380 (Khulays, 63 km)</t>
   </si>
   <si>
     <t>e_w524938770-380_SAU</t>
   </si>
   <si>
-    <t>grid node -- way/524938770-380</t>
+    <t>grid node -- way/524938770-380 (Yanbu`, 31 km)</t>
   </si>
   <si>
     <t>e_w582073817-380_SAU</t>
   </si>
   <si>
-    <t>grid node -- way/582073817-380</t>
+    <t>grid node -- way/582073817-380 (Al Qurayyat, 132 km)</t>
   </si>
   <si>
     <t>e_w586137460-380_SAU</t>
   </si>
   <si>
-    <t>grid node -- way/586137460-380</t>
+    <t>grid node -- way/586137460-380 (Najran, 44 km)</t>
   </si>
   <si>
     <t>e_w597093579-380_SAU</t>
   </si>
   <si>
-    <t>grid node -- way/597093579-380</t>
+    <t>grid node -- way/597093579-380 (Hafr al Batin, 13 km)</t>
   </si>
   <si>
     <t>e_w818080067-380_SAU</t>
   </si>
   <si>
-    <t>grid node -- way/818080067-380</t>
+    <t>grid node -- way/818080067-380 (Turayf, 21 km)</t>
   </si>
   <si>
     <t>e_w818155745-380_SAU</t>
   </si>
   <si>
-    <t>grid node -- way/818155745-380</t>
+    <t>grid node -- way/818155745-380 (Tabuk, 132 km)</t>
   </si>
   <si>
     <t>e_w820233467-380_SAU</t>
   </si>
   <si>
-    <t>grid node -- way/820233467-380</t>
+    <t>grid node -- way/820233467-380 (Ad Darb, 17 km)</t>
   </si>
   <si>
     <t>e_w899264357-380_SAU</t>
   </si>
   <si>
-    <t>grid node -- way/899264357-380</t>
+    <t>grid node -- way/899264357-380 (Riyadh, 112 km)</t>
   </si>
   <si>
     <t>e_w900157271-380_SAU</t>
   </si>
   <si>
-    <t>grid node -- way/900157271-380</t>
+    <t>grid node -- way/900157271-380 (Al Hufuf, 38 km)</t>
   </si>
 </sst>
 </file>
@@ -7805,7 +7805,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A7B8280-4A32-4CE8-AF65-B42BF6328E51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7E5159F-A53D-4B24-B862-D8917B2C376C}">
   <dimension ref="B3:I23"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_SAU_grids_kan25/SysSettings.xlsx
+++ b/VerveStacks_SAU_grids_kan25/SysSettings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SAU_grids_kan25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA0CFBA-99E2-4686-B261-DDF5890FED01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42CAEF0D-8620-4E9F-B749-251B0940F9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7805,7 +7805,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7E5159F-A53D-4B24-B862-D8917B2C376C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73C2617A-F5EA-4942-B480-20E5EF7007E5}">
   <dimension ref="B3:I23"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_SAU_grids_kan25/SysSettings.xlsx
+++ b/VerveStacks_SAU_grids_kan25/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SAU_grids_kan25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42CAEF0D-8620-4E9F-B749-251B0940F9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35CF94C-A93B-4129-A11B-7D977915AAF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7805,7 +7805,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73C2617A-F5EA-4942-B480-20E5EF7007E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85050850-5A7B-45B8-A4ED-800E721C911D}">
   <dimension ref="B3:I23"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
